--- a/tools/technology-capital-allocation/technology-capital-allocation-workbook.xlsx
+++ b/tools/technology-capital-allocation/technology-capital-allocation-workbook.xlsx
@@ -74,19 +74,19 @@
     <t>Zero-Based Review</t>
   </si>
   <si>
-    <t>Once a year, walk every active investment and ask honestly: would we start this today? A 'No' needs a wind-down date, not silence.</t>
+    <t>Once a year, walk every active investment and ask: would we start this today? A 'No' needs a wind-down date rather than silence.</t>
   </si>
   <si>
     <t>Real Options Tracker</t>
   </si>
   <si>
-    <t>Horizon 3 bets staged as options, not full commitments. Fund the next decision point, not the whole initiative, until uncertainty resolves.</t>
+    <t>Horizon 3 bets staged as options rather than full commitments. Fund the next decision point rather than the whole initiative, until uncertainty resolves.</t>
   </si>
   <si>
     <t>3-Year Projection</t>
   </si>
   <si>
-    <t>How the allocation mix is meant to shift over three years, not just this year's number.</t>
+    <t>How the allocation mix is meant to shift over three years, beyond this year's number.</t>
   </si>
   <si>
     <t>Legend</t>
@@ -170,13 +170,13 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Target % should sum to 100%. If it doesn't, the allocation isn't actually decided yet, just aspirational.</t>
+    <t>Target % should sum to 100%. If it doesn't, the allocation is still aspirational rather than decided.</t>
   </si>
   <si>
     <t>$10M Less: Pre-Ranked Cut List</t>
   </si>
   <si>
-    <t>Built before you need it, per the page's core argument. Rank in the order you'd actually cut, first to last.</t>
+    <t>Built before you need it, per the page's core argument. Rank in the order you would cut, first to last.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -251,13 +251,13 @@
     <t>Only after items 1-5 are exhausted</t>
   </si>
   <si>
-    <t>A cut list with no stated consequence isn't a plan, it's a guess. Fill the consequence column honestly, including “near-zero” where that's true.</t>
+    <t>A cut list with no stated consequence is a guess. Fill the consequence column candidly, including “near-zero” where that's true.</t>
   </si>
   <si>
     <t>$10M More: Pre-Ranked Funding List</t>
   </si>
   <si>
-    <t>The mirror image of the cut list. A windfall gets deployed deliberately, not absorbed by whoever asks loudest.</t>
+    <t>The mirror image of the cut list. A windfall gets deployed deliberately instead of absorbed by whoever asks loudest.</t>
   </si>
   <si>
     <t>Horizon</t>
@@ -278,7 +278,7 @@
     <t>H2</t>
   </si>
   <si>
-    <t>So that the next 5 integrations ship in weeks, not quarters, measured by integration lead time</t>
+    <t>So that the next 5 integrations ship in weeks rather than quarters, measured by integration lead time</t>
   </si>
   <si>
     <t>Dedicated security headcount</t>
@@ -365,10 +365,10 @@
     <t>Core to three of the four Grow-horizon initiatives currently funded</t>
   </si>
   <si>
-    <t>An honest “N” with no wind-down date is worse than not running this exercise at all; it documents the problem without committing to fix it.</t>
-  </si>
-  <si>
-    <t>Horizon 3 bets staged as options. Fund the next decision point, not the whole initiative, until uncertainty resolves.</t>
+    <t>An “N” with no wind-down date is worse than not running this exercise at all; it documents the problem without committing to fix it.</t>
+  </si>
+  <si>
+    <t>Horizon 3 bets staged as options. Fund the next decision point rather than the whole initiative, until uncertainty resolves.</t>
   </si>
   <si>
     <t>Bet</t>
@@ -425,7 +425,7 @@
     <t>3-Year Allocation Projection</t>
   </si>
   <si>
-    <t>How the mix is meant to shift over three years, not just this year's number.</t>
+    <t>How the mix is meant to shift over three years, beyond this year's number.</t>
   </si>
   <si>
     <t>Total Budget, Year 1</t>
